--- a/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="132">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -352,9 +352,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t xml:space="preserve">処理結果ステータス	</t>
@@ -428,10 +425,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -476,9 +473,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,7 +495,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,32 +508,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -540,6 +519,22 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -566,9 +561,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -582,8 +576,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -598,6 +593,22 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
@@ -607,21 +618,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -654,7 +651,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,13 +699,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,7 +717,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,19 +741,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,7 +771,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +789,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,67 +801,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,7 +813,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,11 +986,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1013,11 +1008,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1046,15 +1047,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1070,17 +1062,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1089,155 +1086,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1448,12 +1445,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1561,9 +1552,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2294,442 +2282,442 @@
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="3.66666666666667" style="113"/>
-    <col min="2" max="2" width="5.11111111111111" style="114" customWidth="1"/>
-    <col min="3" max="3" width="12.3333333333333" style="113" customWidth="1"/>
-    <col min="4" max="4" width="10.3333333333333" style="113" customWidth="1"/>
-    <col min="5" max="5" width="66.1111111111111" style="113" customWidth="1"/>
-    <col min="6" max="16384" width="3.66666666666667" style="113"/>
+    <col min="1" max="1" width="3.66666666666667" style="110"/>
+    <col min="2" max="2" width="5.11111111111111" style="111" customWidth="1"/>
+    <col min="3" max="3" width="12.3333333333333" style="110" customWidth="1"/>
+    <col min="4" max="4" width="10.3333333333333" style="110" customWidth="1"/>
+    <col min="5" max="5" width="66.1111111111111" style="110" customWidth="1"/>
+    <col min="6" max="16384" width="3.66666666666667" style="110"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="113" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="118">
+      <c r="C3" s="115">
         <v>45636</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="119" t="s">
+      <c r="E3" s="116" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="117"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="117"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="117"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="117"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="119"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="117"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="117"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="117"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="117"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="117"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
+      <c r="B12" s="114"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="117"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="117"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="117"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="117"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="117"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="117"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="117"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="117"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="117"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="117"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="117"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="117"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="117"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="117"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
+      <c r="B26" s="114"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="117"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="117"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="117"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
+      <c r="B29" s="114"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="117"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
+      <c r="B30" s="114"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="117"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
+      <c r="B31" s="114"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="117"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
+      <c r="B32" s="114"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="117"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="117"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
+      <c r="B34" s="114"/>
+      <c r="C34" s="116"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="117"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="116"/>
+      <c r="D35" s="116"/>
+      <c r="E35" s="116"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="117"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
+      <c r="B36" s="114"/>
+      <c r="C36" s="116"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="117"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
+      <c r="B37" s="114"/>
+      <c r="C37" s="116"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="117"/>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
+      <c r="B38" s="114"/>
+      <c r="C38" s="116"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="117"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
+      <c r="B39" s="114"/>
+      <c r="C39" s="116"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="117"/>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
+      <c r="B40" s="114"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="117"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
+      <c r="B41" s="114"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116"/>
+      <c r="E41" s="116"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="117"/>
-      <c r="C42" s="119"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="119"/>
+      <c r="B42" s="114"/>
+      <c r="C42" s="116"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="116"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="117"/>
-      <c r="C43" s="119"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="119"/>
+      <c r="B43" s="114"/>
+      <c r="C43" s="116"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="116"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="117"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
+      <c r="B44" s="114"/>
+      <c r="C44" s="116"/>
+      <c r="D44" s="116"/>
+      <c r="E44" s="116"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="117"/>
-      <c r="C45" s="119"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
+      <c r="B45" s="114"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="116"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="117"/>
-      <c r="C46" s="119"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
+      <c r="B46" s="114"/>
+      <c r="C46" s="116"/>
+      <c r="D46" s="116"/>
+      <c r="E46" s="116"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="117"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
+      <c r="B47" s="114"/>
+      <c r="C47" s="116"/>
+      <c r="D47" s="116"/>
+      <c r="E47" s="116"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="117"/>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
+      <c r="B48" s="114"/>
+      <c r="C48" s="116"/>
+      <c r="D48" s="116"/>
+      <c r="E48" s="116"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="117"/>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
+      <c r="B49" s="114"/>
+      <c r="C49" s="116"/>
+      <c r="D49" s="116"/>
+      <c r="E49" s="116"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="117"/>
-      <c r="C50" s="119"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
+      <c r="B50" s="114"/>
+      <c r="C50" s="116"/>
+      <c r="D50" s="116"/>
+      <c r="E50" s="116"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="117"/>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
+      <c r="B51" s="114"/>
+      <c r="C51" s="116"/>
+      <c r="D51" s="116"/>
+      <c r="E51" s="116"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="117"/>
-      <c r="C52" s="119"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
+      <c r="B52" s="114"/>
+      <c r="C52" s="116"/>
+      <c r="D52" s="116"/>
+      <c r="E52" s="116"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="117"/>
-      <c r="C53" s="119"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
+      <c r="B53" s="114"/>
+      <c r="C53" s="116"/>
+      <c r="D53" s="116"/>
+      <c r="E53" s="116"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="117"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
+      <c r="B54" s="114"/>
+      <c r="C54" s="116"/>
+      <c r="D54" s="116"/>
+      <c r="E54" s="116"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="117"/>
-      <c r="C55" s="119"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="119"/>
+      <c r="B55" s="114"/>
+      <c r="C55" s="116"/>
+      <c r="D55" s="116"/>
+      <c r="E55" s="116"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="117"/>
-      <c r="C56" s="119"/>
-      <c r="D56" s="119"/>
-      <c r="E56" s="119"/>
+      <c r="B56" s="114"/>
+      <c r="C56" s="116"/>
+      <c r="D56" s="116"/>
+      <c r="E56" s="116"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="117"/>
-      <c r="C57" s="119"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="119"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="116"/>
+      <c r="D57" s="116"/>
+      <c r="E57" s="116"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="117"/>
-      <c r="C58" s="119"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="119"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="116"/>
+      <c r="D58" s="116"/>
+      <c r="E58" s="116"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="117"/>
-      <c r="C59" s="119"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="119"/>
+      <c r="B59" s="114"/>
+      <c r="C59" s="116"/>
+      <c r="D59" s="116"/>
+      <c r="E59" s="116"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="117"/>
-      <c r="C60" s="119"/>
-      <c r="D60" s="119"/>
-      <c r="E60" s="119"/>
+      <c r="B60" s="114"/>
+      <c r="C60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="117"/>
-      <c r="C61" s="119"/>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
+      <c r="B61" s="114"/>
+      <c r="C61" s="116"/>
+      <c r="D61" s="116"/>
+      <c r="E61" s="116"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="117"/>
-      <c r="C62" s="119"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="119"/>
+      <c r="B62" s="114"/>
+      <c r="C62" s="116"/>
+      <c r="D62" s="116"/>
+      <c r="E62" s="116"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="117"/>
-      <c r="C63" s="119"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="119"/>
+      <c r="B63" s="114"/>
+      <c r="C63" s="116"/>
+      <c r="D63" s="116"/>
+      <c r="E63" s="116"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="117"/>
-      <c r="C64" s="119"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
+      <c r="B64" s="114"/>
+      <c r="C64" s="116"/>
+      <c r="D64" s="116"/>
+      <c r="E64" s="116"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="117"/>
-      <c r="C65" s="119"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
+      <c r="B65" s="114"/>
+      <c r="C65" s="116"/>
+      <c r="D65" s="116"/>
+      <c r="E65" s="116"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="117"/>
-      <c r="C66" s="119"/>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
+      <c r="B66" s="114"/>
+      <c r="C66" s="116"/>
+      <c r="D66" s="116"/>
+      <c r="E66" s="116"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="117"/>
-      <c r="C67" s="119"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
+      <c r="B67" s="114"/>
+      <c r="C67" s="116"/>
+      <c r="D67" s="116"/>
+      <c r="E67" s="116"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="117"/>
-      <c r="C68" s="119"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="119"/>
+      <c r="B68" s="114"/>
+      <c r="C68" s="116"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="116"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="117"/>
-      <c r="C69" s="119"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
+      <c r="B69" s="114"/>
+      <c r="C69" s="116"/>
+      <c r="D69" s="116"/>
+      <c r="E69" s="116"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2743,11 +2731,11 @@
   <dimension ref="A1:AH25"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="77"/>
-    <col min="21" max="21" width="5.86666666666667" style="77" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="77"/>
-    <col min="34" max="34" width="13.0148148148148" style="77" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="77"/>
+    <col min="1" max="20" width="3.66666666666667" style="75"/>
+    <col min="21" max="21" width="5.86666666666667" style="75" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="75"/>
+    <col min="34" max="34" width="13.0148148148148" style="75" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="75"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -2763,7 +2751,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="99"/>
+      <c r="K1" s="97"/>
       <c r="L1" s="29" t="s">
         <v>9</v>
       </c>
@@ -2788,17 +2776,17 @@
       </c>
       <c r="Z1" s="40"/>
       <c r="AA1" s="40"/>
-      <c r="AB1" s="109"/>
+      <c r="AB1" s="106"/>
       <c r="AC1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="110"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="121" t="s">
+      <c r="AD1" s="107"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
     </row>
     <row r="2" customHeight="1" spans="1:34">
       <c r="A2" s="7"/>
@@ -2811,7 +2799,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="100"/>
+      <c r="K2" s="98"/>
       <c r="L2" s="33"/>
       <c r="M2" s="34"/>
       <c r="N2" s="34"/>
@@ -2828,13 +2816,13 @@
       <c r="Y2" s="44"/>
       <c r="Z2" s="45"/>
       <c r="AA2" s="45"/>
-      <c r="AB2" s="112"/>
+      <c r="AB2" s="109"/>
       <c r="AC2" s="46"/>
       <c r="AD2" s="51"/>
       <c r="AE2" s="52"/>
       <c r="AF2" s="47"/>
-      <c r="AG2" s="74"/>
-      <c r="AH2" s="74"/>
+      <c r="AG2" s="72"/>
+      <c r="AH2" s="72"/>
     </row>
     <row r="3" customHeight="1" spans="1:34">
       <c r="A3" s="7"/>
@@ -2847,7 +2835,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="100"/>
+      <c r="K3" s="98"/>
       <c r="L3" s="29" t="s">
         <v>13</v>
       </c>
@@ -2872,17 +2860,17 @@
       </c>
       <c r="Z3" s="40"/>
       <c r="AA3" s="40"/>
-      <c r="AB3" s="109"/>
+      <c r="AB3" s="106"/>
       <c r="AC3" s="38" t="s">
         <v>17</v>
       </c>
       <c r="AD3" s="38"/>
       <c r="AE3" s="38"/>
-      <c r="AF3" s="121" t="s">
+      <c r="AF3" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="73"/>
-      <c r="AH3" s="73"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
     </row>
     <row r="4" customHeight="1" spans="1:34">
       <c r="A4" s="9"/>
@@ -2895,7 +2883,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
-      <c r="K4" s="101"/>
+      <c r="K4" s="99"/>
       <c r="L4" s="33"/>
       <c r="M4" s="34"/>
       <c r="N4" s="34"/>
@@ -2912,819 +2900,819 @@
       <c r="Y4" s="44"/>
       <c r="Z4" s="45"/>
       <c r="AA4" s="45"/>
-      <c r="AB4" s="112"/>
+      <c r="AB4" s="109"/>
       <c r="AC4" s="38"/>
       <c r="AD4" s="38"/>
       <c r="AE4" s="38"/>
       <c r="AF4" s="47"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
+      <c r="AG4" s="72"/>
+      <c r="AH4" s="72"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="81" t="s">
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="100"/>
+      <c r="U5" s="100"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="100"/>
+      <c r="X5" s="100"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="100"/>
+      <c r="AD5" s="100"/>
+      <c r="AE5" s="100"/>
+      <c r="AF5" s="100"/>
+      <c r="AG5" s="100"/>
+      <c r="AH5" s="100"/>
     </row>
     <row r="6" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="81" t="s">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="102"/>
-      <c r="S6" s="102"/>
-      <c r="T6" s="102"/>
-      <c r="U6" s="102"/>
-      <c r="V6" s="102"/>
-      <c r="W6" s="102"/>
-      <c r="X6" s="102"/>
-      <c r="Y6" s="102"/>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="102"/>
-      <c r="AB6" s="102"/>
-      <c r="AC6" s="102"/>
-      <c r="AD6" s="102"/>
-      <c r="AE6" s="102"/>
-      <c r="AF6" s="102"/>
-      <c r="AG6" s="102"/>
-      <c r="AH6" s="102"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="100"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="100"/>
+      <c r="S6" s="100"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="100"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="100"/>
+      <c r="AA6" s="100"/>
+      <c r="AB6" s="100"/>
+      <c r="AC6" s="100"/>
+      <c r="AD6" s="100"/>
+      <c r="AE6" s="100"/>
+      <c r="AF6" s="100"/>
+      <c r="AG6" s="100"/>
+      <c r="AH6" s="100"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="81" t="s">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="100"/>
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100"/>
+      <c r="R7" s="100"/>
+      <c r="S7" s="100"/>
+      <c r="T7" s="100"/>
+      <c r="U7" s="100"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="100"/>
+      <c r="Y7" s="100"/>
+      <c r="Z7" s="100"/>
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="100"/>
+      <c r="AD7" s="100"/>
+      <c r="AE7" s="100"/>
+      <c r="AF7" s="100"/>
+      <c r="AG7" s="100"/>
+      <c r="AH7" s="100"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="81" t="s">
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="102"/>
-      <c r="AF8" s="102"/>
-      <c r="AG8" s="102"/>
-      <c r="AH8" s="102"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="100"/>
+      <c r="O8" s="100"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="100"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="100"/>
+      <c r="U8" s="100"/>
+      <c r="V8" s="100"/>
+      <c r="W8" s="100"/>
+      <c r="X8" s="100"/>
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="100"/>
+      <c r="AA8" s="100"/>
+      <c r="AB8" s="100"/>
+      <c r="AC8" s="100"/>
+      <c r="AD8" s="100"/>
+      <c r="AE8" s="100"/>
+      <c r="AF8" s="100"/>
+      <c r="AG8" s="100"/>
+      <c r="AH8" s="100"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="102"/>
-      <c r="S9" s="102"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="102"/>
-      <c r="V9" s="102"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="102"/>
-      <c r="Y9" s="102"/>
-      <c r="Z9" s="102"/>
-      <c r="AA9" s="102"/>
-      <c r="AB9" s="102"/>
-      <c r="AC9" s="102"/>
-      <c r="AD9" s="102"/>
-      <c r="AE9" s="102"/>
-      <c r="AF9" s="102"/>
-      <c r="AG9" s="102"/>
-      <c r="AH9" s="102"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="100"/>
+      <c r="Q9" s="100"/>
+      <c r="R9" s="100"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="100"/>
+      <c r="U9" s="100"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="100"/>
+      <c r="X9" s="100"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="100"/>
+      <c r="AA9" s="100"/>
+      <c r="AB9" s="100"/>
+      <c r="AC9" s="100"/>
+      <c r="AD9" s="100"/>
+      <c r="AE9" s="100"/>
+      <c r="AF9" s="100"/>
+      <c r="AG9" s="100"/>
+      <c r="AH9" s="100"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="85" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="103"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="103"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="103"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="103"/>
-      <c r="T10" s="103"/>
-      <c r="U10" s="103"/>
-      <c r="V10" s="103"/>
-      <c r="W10" s="103"/>
-      <c r="X10" s="103"/>
-      <c r="Y10" s="103"/>
-      <c r="Z10" s="103"/>
-      <c r="AA10" s="103"/>
-      <c r="AB10" s="103"/>
-      <c r="AC10" s="103"/>
-      <c r="AD10" s="103"/>
-      <c r="AE10" s="103"/>
-      <c r="AF10" s="103"/>
-      <c r="AG10" s="103"/>
-      <c r="AH10" s="103"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="101"/>
+      <c r="T10" s="101"/>
+      <c r="U10" s="101"/>
+      <c r="V10" s="101"/>
+      <c r="W10" s="101"/>
+      <c r="X10" s="101"/>
+      <c r="Y10" s="101"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="101"/>
+      <c r="AC10" s="101"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="101"/>
+      <c r="AG10" s="101"/>
+      <c r="AH10" s="101"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="87"/>
-      <c r="M11" s="87"/>
-      <c r="N11" s="87"/>
-      <c r="O11" s="87"/>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="87"/>
-      <c r="AF11" s="87"/>
-      <c r="AG11" s="87"/>
-      <c r="AH11" s="87"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="85"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="85"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="89"/>
-      <c r="O12" s="89"/>
-      <c r="P12" s="89"/>
-      <c r="Q12" s="89"/>
-      <c r="R12" s="89"/>
-      <c r="S12" s="89"/>
-      <c r="T12" s="89"/>
-      <c r="U12" s="89"/>
-      <c r="V12" s="89"/>
-      <c r="W12" s="89"/>
-      <c r="X12" s="89"/>
-      <c r="Y12" s="89"/>
-      <c r="Z12" s="89"/>
-      <c r="AA12" s="89"/>
-      <c r="AB12" s="89"/>
-      <c r="AC12" s="89"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="89"/>
-      <c r="AF12" s="89"/>
-      <c r="AG12" s="89"/>
-      <c r="AH12" s="89"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="87"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="87"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="87"/>
+      <c r="T12" s="87"/>
+      <c r="U12" s="87"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="87"/>
+      <c r="X12" s="87"/>
+      <c r="Y12" s="87"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="87"/>
+      <c r="AB12" s="87"/>
+      <c r="AC12" s="87"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="87"/>
+      <c r="AF12" s="87"/>
+      <c r="AG12" s="87"/>
+      <c r="AH12" s="87"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="89"/>
-      <c r="U13" s="89"/>
-      <c r="V13" s="89"/>
-      <c r="W13" s="89"/>
-      <c r="X13" s="89"/>
-      <c r="Y13" s="89"/>
-      <c r="Z13" s="89"/>
-      <c r="AA13" s="89"/>
-      <c r="AB13" s="89"/>
-      <c r="AC13" s="89"/>
-      <c r="AD13" s="89"/>
-      <c r="AE13" s="89"/>
-      <c r="AF13" s="89"/>
-      <c r="AG13" s="89"/>
-      <c r="AH13" s="89"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="87"/>
+      <c r="U13" s="87"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="87"/>
+      <c r="X13" s="87"/>
+      <c r="Y13" s="87"/>
+      <c r="Z13" s="87"/>
+      <c r="AA13" s="87"/>
+      <c r="AB13" s="87"/>
+      <c r="AC13" s="87"/>
+      <c r="AD13" s="87"/>
+      <c r="AE13" s="87"/>
+      <c r="AF13" s="87"/>
+      <c r="AG13" s="87"/>
+      <c r="AH13" s="87"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="89"/>
-      <c r="P14" s="89"/>
-      <c r="Q14" s="89"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="89"/>
-      <c r="T14" s="89"/>
-      <c r="U14" s="89"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="89"/>
-      <c r="X14" s="89"/>
-      <c r="Y14" s="89"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="89"/>
-      <c r="AB14" s="89"/>
-      <c r="AC14" s="89"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="89"/>
-      <c r="AG14" s="89"/>
-      <c r="AH14" s="89"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="87"/>
+      <c r="M14" s="87"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="87"/>
+      <c r="T14" s="87"/>
+      <c r="U14" s="87"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="87"/>
+      <c r="X14" s="87"/>
+      <c r="Y14" s="87"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="87"/>
+      <c r="AB14" s="87"/>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="87"/>
+      <c r="AF14" s="87"/>
+      <c r="AG14" s="87"/>
+      <c r="AH14" s="87"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="89"/>
-      <c r="Q15" s="89"/>
-      <c r="R15" s="89"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="89"/>
-      <c r="U15" s="89"/>
-      <c r="V15" s="89"/>
-      <c r="W15" s="89"/>
-      <c r="X15" s="89"/>
-      <c r="Y15" s="89"/>
-      <c r="Z15" s="89"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="89"/>
-      <c r="AC15" s="89"/>
-      <c r="AD15" s="89"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="89"/>
-      <c r="AG15" s="89"/>
-      <c r="AH15" s="89"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="87"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="87"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="87"/>
+      <c r="AD15" s="87"/>
+      <c r="AE15" s="87"/>
+      <c r="AF15" s="87"/>
+      <c r="AG15" s="87"/>
+      <c r="AH15" s="87"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A16" s="88"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="89"/>
-      <c r="O16" s="89"/>
-      <c r="P16" s="89"/>
-      <c r="Q16" s="89"/>
-      <c r="R16" s="89"/>
-      <c r="S16" s="89"/>
-      <c r="T16" s="89"/>
-      <c r="U16" s="89"/>
-      <c r="V16" s="89"/>
-      <c r="W16" s="89"/>
-      <c r="X16" s="89"/>
-      <c r="Y16" s="89"/>
-      <c r="Z16" s="89"/>
-      <c r="AA16" s="89"/>
-      <c r="AB16" s="89"/>
-      <c r="AC16" s="89"/>
-      <c r="AD16" s="89"/>
-      <c r="AE16" s="89"/>
-      <c r="AF16" s="89"/>
-      <c r="AG16" s="89"/>
-      <c r="AH16" s="89"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="87"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="87"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="87"/>
+      <c r="X16" s="87"/>
+      <c r="Y16" s="87"/>
+      <c r="Z16" s="87"/>
+      <c r="AA16" s="87"/>
+      <c r="AB16" s="87"/>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="87"/>
+      <c r="AE16" s="87"/>
+      <c r="AF16" s="87"/>
+      <c r="AG16" s="87"/>
+      <c r="AH16" s="87"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A17" s="88"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="89"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="89"/>
-      <c r="O17" s="89"/>
-      <c r="P17" s="89"/>
-      <c r="Q17" s="89"/>
-      <c r="R17" s="89"/>
-      <c r="S17" s="89"/>
-      <c r="T17" s="89"/>
-      <c r="U17" s="89"/>
-      <c r="V17" s="89"/>
-      <c r="W17" s="89"/>
-      <c r="X17" s="89"/>
-      <c r="Y17" s="89"/>
-      <c r="Z17" s="89"/>
-      <c r="AA17" s="89"/>
-      <c r="AB17" s="89"/>
-      <c r="AC17" s="89"/>
-      <c r="AD17" s="89"/>
-      <c r="AE17" s="89"/>
-      <c r="AF17" s="89"/>
-      <c r="AG17" s="89"/>
-      <c r="AH17" s="89"/>
+      <c r="A17" s="86"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="87"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="87"/>
+      <c r="U17" s="87"/>
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="87"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="87"/>
+      <c r="AE17" s="87"/>
+      <c r="AF17" s="87"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="87"/>
     </row>
     <row r="18" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="89"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="89"/>
-      <c r="T18" s="89"/>
-      <c r="U18" s="89"/>
-      <c r="V18" s="89"/>
-      <c r="W18" s="89"/>
-      <c r="X18" s="89"/>
-      <c r="Y18" s="89"/>
-      <c r="Z18" s="89"/>
-      <c r="AA18" s="89"/>
-      <c r="AB18" s="89"/>
-      <c r="AC18" s="89"/>
-      <c r="AD18" s="89"/>
-      <c r="AE18" s="89"/>
-      <c r="AF18" s="89"/>
-      <c r="AG18" s="89"/>
-      <c r="AH18" s="89"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="87"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="87"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="87"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="87"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="87"/>
+      <c r="AE18" s="87"/>
+      <c r="AF18" s="87"/>
+      <c r="AG18" s="87"/>
+      <c r="AH18" s="87"/>
     </row>
     <row r="19" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="89"/>
-      <c r="N19" s="89"/>
-      <c r="O19" s="89"/>
-      <c r="P19" s="89"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="89"/>
-      <c r="S19" s="89"/>
-      <c r="T19" s="89"/>
-      <c r="U19" s="89"/>
-      <c r="V19" s="89"/>
-      <c r="W19" s="89"/>
-      <c r="X19" s="89"/>
-      <c r="Y19" s="89"/>
-      <c r="Z19" s="89"/>
-      <c r="AA19" s="89"/>
-      <c r="AB19" s="89"/>
-      <c r="AC19" s="89"/>
-      <c r="AD19" s="89"/>
-      <c r="AE19" s="89"/>
-      <c r="AF19" s="89"/>
-      <c r="AG19" s="89"/>
-      <c r="AH19" s="89"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="87"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="87"/>
+      <c r="T19" s="87"/>
+      <c r="U19" s="87"/>
+      <c r="V19" s="87"/>
+      <c r="W19" s="87"/>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="87"/>
+      <c r="Z19" s="87"/>
+      <c r="AA19" s="87"/>
+      <c r="AB19" s="87"/>
+      <c r="AC19" s="87"/>
+      <c r="AD19" s="87"/>
+      <c r="AE19" s="87"/>
+      <c r="AF19" s="87"/>
+      <c r="AG19" s="87"/>
+      <c r="AH19" s="87"/>
     </row>
     <row r="20" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="89"/>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="89"/>
-      <c r="S20" s="89"/>
-      <c r="T20" s="89"/>
-      <c r="U20" s="89"/>
-      <c r="V20" s="89"/>
-      <c r="W20" s="89"/>
-      <c r="X20" s="89"/>
-      <c r="Y20" s="89"/>
-      <c r="Z20" s="89"/>
-      <c r="AA20" s="89"/>
-      <c r="AB20" s="89"/>
-      <c r="AC20" s="89"/>
-      <c r="AD20" s="89"/>
-      <c r="AE20" s="89"/>
-      <c r="AF20" s="89"/>
-      <c r="AG20" s="89"/>
-      <c r="AH20" s="89"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="87"/>
+      <c r="N20" s="87"/>
+      <c r="O20" s="87"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="87"/>
+      <c r="U20" s="87"/>
+      <c r="V20" s="87"/>
+      <c r="W20" s="87"/>
+      <c r="X20" s="87"/>
+      <c r="Y20" s="87"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="87"/>
+      <c r="AB20" s="87"/>
+      <c r="AC20" s="87"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="87"/>
+      <c r="AF20" s="87"/>
+      <c r="AG20" s="87"/>
+      <c r="AH20" s="87"/>
     </row>
     <row r="21" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="89"/>
-      <c r="N21" s="89"/>
-      <c r="O21" s="89"/>
-      <c r="P21" s="89"/>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="89"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="89"/>
-      <c r="W21" s="89"/>
-      <c r="X21" s="89"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="89"/>
-      <c r="AA21" s="89"/>
-      <c r="AB21" s="89"/>
-      <c r="AC21" s="89"/>
-      <c r="AD21" s="89"/>
-      <c r="AE21" s="89"/>
-      <c r="AF21" s="89"/>
-      <c r="AG21" s="89"/>
-      <c r="AH21" s="89"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="87"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="87"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="87"/>
+      <c r="U21" s="87"/>
+      <c r="V21" s="87"/>
+      <c r="W21" s="87"/>
+      <c r="X21" s="87"/>
+      <c r="Y21" s="87"/>
+      <c r="Z21" s="87"/>
+      <c r="AA21" s="87"/>
+      <c r="AB21" s="87"/>
+      <c r="AC21" s="87"/>
+      <c r="AD21" s="87"/>
+      <c r="AE21" s="87"/>
+      <c r="AF21" s="87"/>
+      <c r="AG21" s="87"/>
+      <c r="AH21" s="87"/>
     </row>
     <row r="22" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="89"/>
-      <c r="P22" s="89"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
+      <c r="A22" s="86"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="87"/>
+      <c r="P22" s="87"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="87"/>
+      <c r="U22" s="87"/>
+      <c r="V22" s="87"/>
+      <c r="W22" s="87"/>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="87"/>
+      <c r="Z22" s="87"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="87"/>
+      <c r="AC22" s="87"/>
+      <c r="AD22" s="87"/>
+      <c r="AE22" s="87"/>
+      <c r="AF22" s="87"/>
+      <c r="AG22" s="87"/>
+      <c r="AH22" s="87"/>
     </row>
     <row r="23" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="90"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="91"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="91"/>
-      <c r="AA23" s="91"/>
-      <c r="AB23" s="91"/>
-      <c r="AC23" s="91"/>
-      <c r="AD23" s="91"/>
-      <c r="AE23" s="91"/>
-      <c r="AF23" s="91"/>
-      <c r="AG23" s="91"/>
-      <c r="AH23" s="91"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="89"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="89"/>
+      <c r="X23" s="89"/>
+      <c r="Y23" s="89"/>
+      <c r="Z23" s="89"/>
+      <c r="AA23" s="89"/>
+      <c r="AB23" s="89"/>
+      <c r="AC23" s="89"/>
+      <c r="AD23" s="89"/>
+      <c r="AE23" s="89"/>
+      <c r="AF23" s="89"/>
+      <c r="AG23" s="89"/>
+      <c r="AH23" s="89"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="92" t="s">
+      <c r="B24" s="91"/>
+      <c r="C24" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="104" t="s">
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="104" t="s">
+      <c r="L24" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="104" t="s">
+      <c r="M24" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="92" t="s">
+      <c r="N24" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="105" t="s">
+      <c r="O24" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="105"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="105"/>
-      <c r="T24" s="105"/>
-      <c r="U24" s="105"/>
-      <c r="V24" s="105"/>
-      <c r="W24" s="105"/>
-      <c r="X24" s="105"/>
-      <c r="Y24" s="105"/>
-      <c r="Z24" s="105"/>
-      <c r="AA24" s="105"/>
-      <c r="AB24" s="105"/>
-      <c r="AC24" s="105"/>
-      <c r="AD24" s="105"/>
-      <c r="AE24" s="105"/>
-      <c r="AF24" s="105"/>
-      <c r="AG24" s="105"/>
-      <c r="AH24" s="105"/>
+      <c r="P24" s="103"/>
+      <c r="Q24" s="103"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="103"/>
+      <c r="U24" s="103"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="103"/>
+      <c r="X24" s="103"/>
+      <c r="Y24" s="103"/>
+      <c r="Z24" s="103"/>
+      <c r="AA24" s="103"/>
+      <c r="AB24" s="103"/>
+      <c r="AC24" s="103"/>
+      <c r="AD24" s="103"/>
+      <c r="AE24" s="103"/>
+      <c r="AF24" s="103"/>
+      <c r="AG24" s="103"/>
+      <c r="AH24" s="103"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="95">
+      <c r="A25" s="93">
         <v>1</v>
       </c>
-      <c r="B25" s="96"/>
-      <c r="C25" s="97" t="s">
+      <c r="B25" s="94"/>
+      <c r="C25" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="106" t="s">
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="106" t="s">
+      <c r="L25" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="M25" s="106" t="s">
+      <c r="M25" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="107"/>
-      <c r="O25" s="108"/>
-      <c r="P25" s="108"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="108"/>
-      <c r="S25" s="108"/>
-      <c r="T25" s="108"/>
-      <c r="U25" s="108"/>
-      <c r="V25" s="108"/>
-      <c r="W25" s="108"/>
-      <c r="X25" s="108"/>
-      <c r="Y25" s="108"/>
-      <c r="Z25" s="108"/>
-      <c r="AA25" s="108"/>
-      <c r="AB25" s="108"/>
-      <c r="AC25" s="108"/>
-      <c r="AD25" s="108"/>
-      <c r="AE25" s="108"/>
-      <c r="AF25" s="108"/>
-      <c r="AG25" s="108"/>
-      <c r="AH25" s="108"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="104"/>
+      <c r="S25" s="104"/>
+      <c r="T25" s="104"/>
+      <c r="U25" s="104"/>
+      <c r="V25" s="104"/>
+      <c r="W25" s="104"/>
+      <c r="X25" s="104"/>
+      <c r="Y25" s="104"/>
+      <c r="Z25" s="104"/>
+      <c r="AA25" s="104"/>
+      <c r="AB25" s="104"/>
+      <c r="AC25" s="104"/>
+      <c r="AD25" s="104"/>
+      <c r="AE25" s="104"/>
+      <c r="AF25" s="104"/>
+      <c r="AG25" s="104"/>
+      <c r="AH25" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -3826,10 +3814,10 @@
       <c r="W1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="121" t="s">
+      <c r="X1" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="73"/>
+      <c r="Y1" s="71"/>
     </row>
     <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="7"/>
@@ -3856,7 +3844,7 @@
       <c r="V2" s="45"/>
       <c r="W2" s="46"/>
       <c r="X2" s="47"/>
-      <c r="Y2" s="74"/>
+      <c r="Y2" s="72"/>
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="7"/>
@@ -3892,10 +3880,10 @@
       <c r="W3" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="121" t="s">
+      <c r="X3" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="73"/>
+      <c r="Y3" s="71"/>
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="9"/>
@@ -3922,7 +3910,7 @@
       <c r="V4" s="45"/>
       <c r="W4" s="38"/>
       <c r="X4" s="47"/>
-      <c r="Y4" s="74"/>
+      <c r="Y4" s="72"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="11" t="s">
@@ -4171,7 +4159,7 @@
         <v>52</v>
       </c>
       <c r="P13" s="66"/>
-      <c r="Q13" s="122" t="s">
+      <c r="Q13" s="119" t="s">
         <v>68</v>
       </c>
       <c r="R13" s="18"/>
@@ -4191,7 +4179,7 @@
       <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="119" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="18"/>
@@ -4226,7 +4214,7 @@
       <c r="X14" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="Y14" s="75"/>
+      <c r="Y14" s="73"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A15" s="18">
@@ -4340,12 +4328,12 @@
       <c r="Q17" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="71"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="28"/>
       <c r="X17" s="26" t="s">
         <v>86</v>
       </c>
@@ -4488,10 +4476,10 @@
       </c>
       <c r="V21" s="18"/>
       <c r="W21" s="18"/>
-      <c r="X21" s="72">
+      <c r="X21" s="70">
         <v>5</v>
       </c>
-      <c r="Y21" s="76"/>
+      <c r="Y21" s="74"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A22" s="18">
@@ -4520,7 +4508,7 @@
         <v>52</v>
       </c>
       <c r="P22" s="66"/>
-      <c r="Q22" s="122" t="s">
+      <c r="Q22" s="119" t="s">
         <v>94</v>
       </c>
       <c r="R22" s="18"/>
@@ -4563,7 +4551,7 @@
         <v>52</v>
       </c>
       <c r="P23" s="66"/>
-      <c r="Q23" s="122" t="s">
+      <c r="Q23" s="119" t="s">
         <v>94</v>
       </c>
       <c r="R23" s="18"/>
@@ -4574,10 +4562,10 @@
       </c>
       <c r="V23" s="18"/>
       <c r="W23" s="18"/>
-      <c r="X23" s="72">
+      <c r="X23" s="70">
         <v>1</v>
       </c>
-      <c r="Y23" s="76"/>
+      <c r="Y23" s="74"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A24" s="18">
@@ -4661,7 +4649,7 @@
       <c r="X25" s="68">
         <v>20</v>
       </c>
-      <c r="Y25" s="75"/>
+      <c r="Y25" s="73"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A26" s="18">
@@ -4899,7 +4887,7 @@
       <c r="T1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="121" t="s">
+      <c r="U1" s="118" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="43"/>
@@ -4959,7 +4947,7 @@
       <c r="T3" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="121" t="s">
+      <c r="U3" s="118" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="43"/>
@@ -5123,25 +5111,25 @@
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
-      <c r="I9" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="122" t="s">
+      <c r="I9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
-      <c r="P9" s="122" t="s">
-        <v>111</v>
+      <c r="P9" s="119" t="s">
+        <v>110</v>
       </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
       <c r="T9" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
@@ -5151,7 +5139,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -5159,25 +5147,25 @@
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="122" t="s">
+      <c r="I10" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
-      <c r="P10" s="122" t="s">
-        <v>114</v>
+      <c r="P10" s="119" t="s">
+        <v>113</v>
       </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
       <c r="S10" s="18"/>
       <c r="T10" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
@@ -5208,7 +5196,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:22">
       <c r="A12" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -5273,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -5281,25 +5269,25 @@
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20"/>
-      <c r="I14" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="122" t="s">
+      <c r="I14" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
-      <c r="P14" s="122" t="s">
-        <v>111</v>
+      <c r="P14" s="119" t="s">
+        <v>110</v>
       </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -5317,25 +5305,25 @@
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
-      <c r="I15" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="122" t="s">
+      <c r="I15" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
-      <c r="P15" s="122" t="s">
-        <v>118</v>
+      <c r="P15" s="119" t="s">
+        <v>117</v>
       </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -5345,7 +5333,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -5353,32 +5341,32 @@
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="122" t="s">
+      <c r="I16" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
       <c r="T16" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
     </row>
     <row r="18" customHeight="1" spans="1:22">
       <c r="A18" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -5451,25 +5439,25 @@
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
-      <c r="I20" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="122" t="s">
+      <c r="I20" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
-      <c r="P20" s="122" t="s">
-        <v>111</v>
+      <c r="P20" s="119" t="s">
+        <v>110</v>
       </c>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="S20" s="18"/>
       <c r="T20" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
@@ -5479,7 +5467,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -5487,25 +5475,25 @@
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
-      <c r="I21" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="122" t="s">
+      <c r="I21" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
-      <c r="P21" s="122" t="s">
-        <v>118</v>
+      <c r="P21" s="119" t="s">
+        <v>117</v>
       </c>
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U21" s="18"/>
       <c r="V21" s="18"/>
@@ -5515,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
@@ -5523,25 +5511,25 @@
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28"/>
-      <c r="I22" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="122" t="s">
+      <c r="I22" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
       <c r="P22" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
       <c r="S22" s="18"/>
-      <c r="T22" s="122" t="s">
-        <v>126</v>
+      <c r="T22" s="119" t="s">
+        <v>125</v>
       </c>
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
@@ -5551,7 +5539,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
@@ -5559,25 +5547,25 @@
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="122" t="s">
+      <c r="I23" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
       <c r="P23" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
@@ -5587,7 +5575,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
@@ -5595,25 +5583,25 @@
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="122" t="s">
+      <c r="I24" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="119" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
       <c r="T24" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>

--- a/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
@@ -425,10 +425,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -474,28 +474,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,8 +503,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,40 +525,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -576,9 +548,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,14 +565,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -609,6 +580,13 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
@@ -619,6 +597,28 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -651,13 +651,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,61 +663,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,13 +687,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,13 +717,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -789,19 +771,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -813,19 +825,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -984,11 +984,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1008,17 +1014,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1027,7 +1027,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1047,26 +1047,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1081,153 +1066,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">

--- a/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/基本設計書_部品入荷API.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="133">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>◯</t>
+  </si>
+  <si>
+    <t>部品入出庫履歴テーブル</t>
   </si>
   <si>
     <t>リクエスト</t>
@@ -1592,6 +1595,9 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1721,7 +1727,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>部品在庫照会 </a:t>
+            <a:t>部品入荷 </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-GB" altLang="ja-JP" sz="1400">
@@ -1748,15 +1754,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>43180</xdr:rowOff>
+      <xdr:colOff>168910</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>99695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>256540</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>189230</xdr:rowOff>
+      <xdr:colOff>301625</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>245745</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1765,7 +1771,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5467350" y="3872230"/>
+          <a:off x="5512435" y="4439285"/>
           <a:ext cx="1892935" cy="1167130"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
@@ -1975,9 +1981,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>116205</xdr:rowOff>
+      <xdr:colOff>168910</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>172720</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -1990,7 +1996,249 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4624705" y="4451350"/>
-          <a:ext cx="842645" cy="4445"/>
+          <a:ext cx="887730" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>187960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>78740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="フローチャート: 磁気ディスク 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5511800" y="2995930"/>
+          <a:ext cx="1892935" cy="1167130"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t> 部品入出庫履歴</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>テーブル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>227330</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線コネクタ 5"/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="3" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4627880" y="3583940"/>
+          <a:ext cx="883920" cy="815975"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2728,7 +2976,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="20" width="3.66666666666667" style="75"/>
@@ -3714,8 +3962,50 @@
       <c r="AG25" s="104"/>
       <c r="AH25" s="104"/>
     </row>
+    <row r="26" customHeight="1" spans="1:34">
+      <c r="A26" s="93">
+        <v>1</v>
+      </c>
+      <c r="B26" s="94"/>
+      <c r="C26" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" s="104"/>
+      <c r="N26" s="105"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="104"/>
+      <c r="Q26" s="104"/>
+      <c r="R26" s="104"/>
+      <c r="S26" s="104"/>
+      <c r="T26" s="104"/>
+      <c r="U26" s="104"/>
+      <c r="V26" s="104"/>
+      <c r="W26" s="104"/>
+      <c r="X26" s="104"/>
+      <c r="Y26" s="104"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="104"/>
+      <c r="AB26" s="104"/>
+      <c r="AC26" s="104"/>
+      <c r="AD26" s="104"/>
+      <c r="AE26" s="104"/>
+      <c r="AF26" s="104"/>
+      <c r="AG26" s="104"/>
+      <c r="AH26" s="104"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="H5:AH5"/>
     <mergeCell ref="A6:G6"/>
@@ -3734,6 +4024,8 @@
     <mergeCell ref="O24:AH24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="O25:AH25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="O26:AH26"/>
     <mergeCell ref="V3:X4"/>
     <mergeCell ref="AC3:AE4"/>
     <mergeCell ref="AF3:AH4"/>
@@ -3780,7 +4072,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:25">
       <c r="A1" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3914,7 +4206,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -3927,7 +4219,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -3941,7 +4233,7 @@
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
       <c r="T5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U5" s="12" t="s">
         <v>29</v>
@@ -3953,7 +4245,7 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:1">
       <c r="A6" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="23" customHeight="1" spans="1:25">
@@ -3961,7 +4253,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="38"/>
@@ -3971,26 +4263,26 @@
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" s="62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L7" s="63"/>
       <c r="M7" s="63"/>
       <c r="N7" s="64"/>
       <c r="O7" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
       <c r="S7" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T7" s="38"/>
       <c r="U7" s="62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V7" s="63"/>
       <c r="W7" s="63"/>
@@ -4002,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
@@ -4012,10 +4304,10 @@
       <c r="H8" s="55"/>
       <c r="I8" s="55"/>
       <c r="J8" s="55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="27"/>
@@ -4027,11 +4319,11 @@
       <c r="Q8" s="18"/>
       <c r="R8" s="18"/>
       <c r="S8" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T8" s="18"/>
       <c r="U8" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V8" s="27"/>
       <c r="W8" s="27"/>
@@ -4043,7 +4335,7 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:1">
       <c r="A10" s="54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:25">
@@ -4051,41 +4343,41 @@
         <v>31</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
       <c r="E11" s="38"/>
       <c r="F11" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
       <c r="I11" s="38"/>
       <c r="J11" s="38"/>
       <c r="K11" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L11" s="38"/>
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
       <c r="O11" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P11" s="38"/>
       <c r="Q11" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R11" s="61"/>
       <c r="S11" s="61"/>
       <c r="T11" s="61"/>
       <c r="U11" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V11" s="38"/>
       <c r="W11" s="38"/>
       <c r="X11" s="62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y11" s="63"/>
     </row>
@@ -4094,41 +4386,41 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
       <c r="K12" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L12" s="27"/>
       <c r="M12" s="27"/>
       <c r="N12" s="28"/>
       <c r="O12" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P12" s="66"/>
       <c r="Q12" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R12" s="18"/>
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V12" s="18"/>
       <c r="W12" s="18"/>
       <c r="X12" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y12" s="18"/>
     </row>
@@ -4137,41 +4429,41 @@
         <v>2</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
       <c r="I13" s="56"/>
       <c r="J13" s="56"/>
       <c r="K13" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L13" s="27"/>
       <c r="M13" s="27"/>
       <c r="N13" s="28"/>
       <c r="O13" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P13" s="66"/>
-      <c r="Q13" s="119" t="s">
-        <v>68</v>
+      <c r="Q13" s="120" t="s">
+        <v>69</v>
       </c>
       <c r="R13" s="18"/>
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
       <c r="X13" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y13" s="18"/>
     </row>
@@ -4179,31 +4471,31 @@
       <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="119" t="s">
-        <v>71</v>
+      <c r="B14" s="120" t="s">
+        <v>72</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
       <c r="K14" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L14" s="27"/>
       <c r="M14" s="27"/>
       <c r="N14" s="28"/>
       <c r="O14" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P14" s="66"/>
       <c r="Q14" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
@@ -4212,7 +4504,7 @@
       <c r="V14" s="18"/>
       <c r="W14" s="18"/>
       <c r="X14" s="68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y14" s="73"/>
     </row>
@@ -4221,30 +4513,30 @@
         <v>4</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
       <c r="K15" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
       <c r="N15" s="28"/>
       <c r="O15" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P15" s="66"/>
       <c r="Q15" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
@@ -4253,7 +4545,7 @@
       <c r="V15" s="18"/>
       <c r="W15" s="18"/>
       <c r="X15" s="26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y15" s="28"/>
     </row>
@@ -4262,30 +4554,30 @@
         <v>5</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L16" s="27"/>
       <c r="M16" s="27"/>
       <c r="N16" s="28"/>
       <c r="O16" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P16" s="66"/>
       <c r="Q16" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
@@ -4294,7 +4586,7 @@
       <c r="V16" s="18"/>
       <c r="W16" s="18"/>
       <c r="X16" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y16" s="28"/>
     </row>
@@ -4303,30 +4595,30 @@
         <v>6</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
       <c r="N17" s="28"/>
       <c r="O17" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P17" s="66"/>
       <c r="Q17" s="69" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
@@ -4335,7 +4627,7 @@
       <c r="V17" s="27"/>
       <c r="W17" s="28"/>
       <c r="X17" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y17" s="28"/>
     </row>
@@ -4368,7 +4660,7 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A19" s="57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -4400,41 +4692,41 @@
         <v>31</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
       <c r="I20" s="38"/>
       <c r="J20" s="38"/>
       <c r="K20" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
       <c r="O20" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P20" s="38"/>
       <c r="Q20" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R20" s="61"/>
       <c r="S20" s="61"/>
       <c r="T20" s="61"/>
       <c r="U20" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V20" s="38"/>
       <c r="W20" s="38"/>
       <c r="X20" s="62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y20" s="63"/>
     </row>
@@ -4443,36 +4735,36 @@
         <v>1</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="56"/>
       <c r="H21" s="56"/>
       <c r="I21" s="56"/>
       <c r="J21" s="56"/>
       <c r="K21" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="N21" s="28"/>
       <c r="O21" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P21" s="66"/>
       <c r="Q21" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18"/>
       <c r="U21" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V21" s="18"/>
       <c r="W21" s="18"/>
@@ -4486,36 +4778,36 @@
         <v>2</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
       <c r="K22" s="26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
       <c r="N22" s="28"/>
       <c r="O22" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P22" s="66"/>
-      <c r="Q22" s="119" t="s">
-        <v>94</v>
+      <c r="Q22" s="120" t="s">
+        <v>95</v>
       </c>
       <c r="R22" s="18"/>
       <c r="S22" s="18"/>
       <c r="T22" s="18"/>
       <c r="U22" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V22" s="18"/>
       <c r="W22" s="18"/>
@@ -4529,36 +4821,36 @@
         <v>3</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
       <c r="N23" s="28"/>
       <c r="O23" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P23" s="66"/>
-      <c r="Q23" s="119" t="s">
-        <v>94</v>
+      <c r="Q23" s="120" t="s">
+        <v>95</v>
       </c>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18"/>
       <c r="U23" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V23" s="18"/>
       <c r="W23" s="18"/>
@@ -4572,41 +4864,41 @@
         <v>4</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="56"/>
       <c r="H24" s="56"/>
       <c r="I24" s="56"/>
       <c r="J24" s="56"/>
       <c r="K24" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
       <c r="N24" s="28"/>
       <c r="O24" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P24" s="66"/>
       <c r="Q24" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
       <c r="T24" s="18"/>
       <c r="U24" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V24" s="18"/>
       <c r="W24" s="18"/>
       <c r="X24" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="18"/>
     </row>
@@ -4615,26 +4907,26 @@
         <v>5</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
       <c r="K25" s="26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L25" s="27"/>
       <c r="M25" s="27"/>
       <c r="N25" s="28"/>
       <c r="O25" s="65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P25" s="66"/>
       <c r="Q25" s="18"/>
@@ -4642,7 +4934,7 @@
       <c r="S25" s="18"/>
       <c r="T25" s="18"/>
       <c r="U25" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V25" s="18"/>
       <c r="W25" s="18"/>
@@ -4656,20 +4948,20 @@
         <v>6</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L26" s="27"/>
       <c r="M26" s="27"/>
@@ -4677,18 +4969,18 @@
       <c r="O26" s="65"/>
       <c r="P26" s="66"/>
       <c r="Q26" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R26" s="18"/>
       <c r="S26" s="18"/>
       <c r="T26" s="18"/>
       <c r="U26" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
       <c r="X26" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y26" s="28"/>
     </row>
@@ -4856,7 +5148,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:22">
       <c r="A1" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4978,7 +5270,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4990,7 +5282,7 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -5002,7 +5294,7 @@
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R5" s="12" t="s">
         <v>29</v>
@@ -5038,7 +5330,7 @@
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:22">
       <c r="A7" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -5067,7 +5359,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -5076,24 +5368,24 @@
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="37"/>
       <c r="R8" s="37"/>
       <c r="S8" s="37"/>
       <c r="T8" s="46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U8" s="51"/>
       <c r="V8" s="52"/>
@@ -5103,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -5112,24 +5404,24 @@
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
       <c r="I9" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="27"/>
       <c r="L9" s="28"/>
-      <c r="M9" s="119" t="s">
-        <v>52</v>
+      <c r="M9" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
-      <c r="P9" s="119" t="s">
-        <v>110</v>
+      <c r="P9" s="120" t="s">
+        <v>111</v>
       </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
       <c r="T9" s="18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
@@ -5139,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -5148,24 +5440,24 @@
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
       <c r="I10" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
       <c r="L10" s="28"/>
-      <c r="M10" s="119" t="s">
-        <v>52</v>
+      <c r="M10" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
-      <c r="P10" s="119" t="s">
-        <v>113</v>
+      <c r="P10" s="120" t="s">
+        <v>114</v>
       </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
       <c r="S10" s="18"/>
       <c r="T10" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
@@ -5196,7 +5488,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:22">
       <c r="A12" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -5225,7 +5517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -5234,24 +5526,24 @@
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="37"/>
       <c r="R13" s="37"/>
       <c r="S13" s="37"/>
       <c r="T13" s="46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U13" s="51"/>
       <c r="V13" s="52"/>
@@ -5261,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -5270,24 +5562,24 @@
       <c r="G14" s="20"/>
       <c r="H14" s="20"/>
       <c r="I14" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
       <c r="L14" s="28"/>
-      <c r="M14" s="119" t="s">
-        <v>52</v>
+      <c r="M14" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
-      <c r="P14" s="119" t="s">
-        <v>110</v>
+      <c r="P14" s="120" t="s">
+        <v>111</v>
       </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -5297,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -5306,24 +5598,24 @@
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
       <c r="I15" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
       <c r="L15" s="28"/>
-      <c r="M15" s="119" t="s">
-        <v>52</v>
+      <c r="M15" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
-      <c r="P15" s="119" t="s">
-        <v>117</v>
+      <c r="P15" s="120" t="s">
+        <v>118</v>
       </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -5333,7 +5625,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -5342,31 +5634,31 @@
       <c r="G16" s="20"/>
       <c r="H16" s="24"/>
       <c r="I16" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
       <c r="L16" s="28"/>
-      <c r="M16" s="119" t="s">
-        <v>52</v>
+      <c r="M16" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
       <c r="T16" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
     </row>
     <row r="18" customHeight="1" spans="1:22">
       <c r="A18" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -5395,7 +5687,7 @@
         <v>31</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -5404,24 +5696,24 @@
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="I19" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="37"/>
       <c r="R19" s="37"/>
       <c r="S19" s="37"/>
       <c r="T19" s="46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U19" s="51"/>
       <c r="V19" s="52"/>
@@ -5431,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -5440,24 +5732,24 @@
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
       <c r="I20" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
       <c r="L20" s="28"/>
-      <c r="M20" s="119" t="s">
-        <v>52</v>
+      <c r="M20" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
-      <c r="P20" s="119" t="s">
-        <v>110</v>
+      <c r="P20" s="120" t="s">
+        <v>111</v>
       </c>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="S20" s="18"/>
       <c r="T20" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
@@ -5467,7 +5759,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -5476,24 +5768,24 @@
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
       <c r="L21" s="28"/>
-      <c r="M21" s="119" t="s">
-        <v>52</v>
+      <c r="M21" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
-      <c r="P21" s="119" t="s">
-        <v>117</v>
+      <c r="P21" s="120" t="s">
+        <v>118</v>
       </c>
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U21" s="18"/>
       <c r="V21" s="18"/>
@@ -5503,7 +5795,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
@@ -5512,24 +5804,24 @@
       <c r="G22" s="27"/>
       <c r="H22" s="28"/>
       <c r="I22" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
       <c r="L22" s="28"/>
-      <c r="M22" s="119" t="s">
-        <v>52</v>
+      <c r="M22" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
       <c r="P22" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
       <c r="S22" s="18"/>
-      <c r="T22" s="119" t="s">
-        <v>125</v>
+      <c r="T22" s="120" t="s">
+        <v>126</v>
       </c>
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
@@ -5539,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
@@ -5548,24 +5840,24 @@
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
       <c r="I23" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
       <c r="L23" s="28"/>
-      <c r="M23" s="119" t="s">
-        <v>52</v>
+      <c r="M23" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
       <c r="P23" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
@@ -5575,7 +5867,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
@@ -5584,24 +5876,24 @@
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
       <c r="L24" s="28"/>
-      <c r="M24" s="119" t="s">
-        <v>52</v>
+      <c r="M24" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
       <c r="T24" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
